--- a/artfynd/A 21037-2021 artfynd.xlsx
+++ b/artfynd/A 21037-2021 artfynd.xlsx
@@ -529,7 +529,7 @@
       </c>
       <c r="W1" t="inlineStr">
         <is>
-          <t>Församling</t>
+          <t>Socken</t>
         </is>
       </c>
       <c r="X1" t="inlineStr">

--- a/artfynd/A 21037-2021 artfynd.xlsx
+++ b/artfynd/A 21037-2021 artfynd.xlsx
@@ -413,7 +413,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:AY2"/>
+  <dimension ref="A1:AY3"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
@@ -798,6 +798,112 @@
           <t>Elfenbenslav 2008</t>
         </is>
       </c>
+    </row>
+    <row r="3">
+      <c r="A3" t="n">
+        <v>128635232</v>
+      </c>
+      <c r="B3" t="n">
+        <v>86943</v>
+      </c>
+      <c r="D3" t="inlineStr">
+        <is>
+          <t>NT</t>
+        </is>
+      </c>
+      <c r="E3" t="n">
+        <v>3739</v>
+      </c>
+      <c r="F3" t="inlineStr">
+        <is>
+          <t>Persiljespindling</t>
+        </is>
+      </c>
+      <c r="G3" t="inlineStr">
+        <is>
+          <t>Cortinarius sulfurinus</t>
+        </is>
+      </c>
+      <c r="H3" t="inlineStr">
+        <is>
+          <t>Quél.</t>
+        </is>
+      </c>
+      <c r="I3" t="inlineStr"/>
+      <c r="J3" t="inlineStr"/>
+      <c r="K3" t="inlineStr"/>
+      <c r="N3" t="inlineStr"/>
+      <c r="P3" t="inlineStr">
+        <is>
+          <t>Indalsälven, Indalsälven, Jmt</t>
+        </is>
+      </c>
+      <c r="Q3" t="n">
+        <v>569876</v>
+      </c>
+      <c r="R3" t="n">
+        <v>6997515</v>
+      </c>
+      <c r="S3" t="n">
+        <v>10</v>
+      </c>
+      <c r="T3" t="inlineStr">
+        <is>
+          <t>Jämtland</t>
+        </is>
+      </c>
+      <c r="U3" t="inlineStr">
+        <is>
+          <t>Ragunda</t>
+        </is>
+      </c>
+      <c r="V3" t="inlineStr">
+        <is>
+          <t>Jämtland</t>
+        </is>
+      </c>
+      <c r="W3" t="inlineStr">
+        <is>
+          <t>Ragunda</t>
+        </is>
+      </c>
+      <c r="Y3" t="inlineStr">
+        <is>
+          <t>2025-09-23</t>
+        </is>
+      </c>
+      <c r="AA3" t="inlineStr">
+        <is>
+          <t>2025-09-23</t>
+        </is>
+      </c>
+      <c r="AD3" t="b">
+        <v>0</v>
+      </c>
+      <c r="AE3" t="b">
+        <v>0</v>
+      </c>
+      <c r="AF3" t="inlineStr"/>
+      <c r="AG3" t="b">
+        <v>0</v>
+      </c>
+      <c r="AI3" t="inlineStr">
+        <is>
+          <t>Kanten mellan hygge och äldre skog vid sydbrant</t>
+        </is>
+      </c>
+      <c r="AT3" t="inlineStr"/>
+      <c r="AW3" t="inlineStr">
+        <is>
+          <t>Rashid Kadhim</t>
+        </is>
+      </c>
+      <c r="AX3" t="inlineStr">
+        <is>
+          <t>Rashid Kadhim, Fredrik Larsson, Henrik Weibull</t>
+        </is>
+      </c>
+      <c r="AY3" t="inlineStr"/>
     </row>
   </sheetData>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>

--- a/artfynd/A 21037-2021 artfynd.xlsx
+++ b/artfynd/A 21037-2021 artfynd.xlsx
@@ -804,7 +804,7 @@
         <v>128635232</v>
       </c>
       <c r="B3" t="n">
-        <v>86943</v>
+        <v>86948</v>
       </c>
       <c r="D3" t="inlineStr">
         <is>

--- a/artfynd/A 21037-2021 artfynd.xlsx
+++ b/artfynd/A 21037-2021 artfynd.xlsx
@@ -804,7 +804,7 @@
         <v>128635232</v>
       </c>
       <c r="B3" t="n">
-        <v>86948</v>
+        <v>86954</v>
       </c>
       <c r="D3" t="inlineStr">
         <is>

--- a/artfynd/A 21037-2021 artfynd.xlsx
+++ b/artfynd/A 21037-2021 artfynd.xlsx
@@ -804,7 +804,7 @@
         <v>128635232</v>
       </c>
       <c r="B3" t="n">
-        <v>86954</v>
+        <v>86956</v>
       </c>
       <c r="D3" t="inlineStr">
         <is>

--- a/artfynd/A 21037-2021 artfynd.xlsx
+++ b/artfynd/A 21037-2021 artfynd.xlsx
@@ -804,7 +804,7 @@
         <v>128635232</v>
       </c>
       <c r="B3" t="n">
-        <v>86956</v>
+        <v>86983</v>
       </c>
       <c r="D3" t="inlineStr">
         <is>

--- a/artfynd/A 21037-2021 artfynd.xlsx
+++ b/artfynd/A 21037-2021 artfynd.xlsx
@@ -804,7 +804,7 @@
         <v>128635232</v>
       </c>
       <c r="B3" t="n">
-        <v>86983</v>
+        <v>86987</v>
       </c>
       <c r="D3" t="inlineStr">
         <is>

--- a/artfynd/A 21037-2021 artfynd.xlsx
+++ b/artfynd/A 21037-2021 artfynd.xlsx
@@ -804,7 +804,7 @@
         <v>128635232</v>
       </c>
       <c r="B3" t="n">
-        <v>86987</v>
+        <v>86988</v>
       </c>
       <c r="D3" t="inlineStr">
         <is>

--- a/artfynd/A 21037-2021 artfynd.xlsx
+++ b/artfynd/A 21037-2021 artfynd.xlsx
@@ -804,7 +804,7 @@
         <v>128635232</v>
       </c>
       <c r="B3" t="n">
-        <v>86988</v>
+        <v>86992</v>
       </c>
       <c r="D3" t="inlineStr">
         <is>

--- a/artfynd/A 21037-2021 artfynd.xlsx
+++ b/artfynd/A 21037-2021 artfynd.xlsx
@@ -804,7 +804,7 @@
         <v>128635232</v>
       </c>
       <c r="B3" t="n">
-        <v>86992</v>
+        <v>86997</v>
       </c>
       <c r="D3" t="inlineStr">
         <is>

--- a/artfynd/A 21037-2021 artfynd.xlsx
+++ b/artfynd/A 21037-2021 artfynd.xlsx
@@ -804,7 +804,7 @@
         <v>128635232</v>
       </c>
       <c r="B3" t="n">
-        <v>86999</v>
+        <v>87004</v>
       </c>
       <c r="D3" t="inlineStr">
         <is>

--- a/artfynd/A 21037-2021 artfynd.xlsx
+++ b/artfynd/A 21037-2021 artfynd.xlsx
@@ -804,7 +804,7 @@
         <v>128635232</v>
       </c>
       <c r="B3" t="n">
-        <v>87004</v>
+        <v>87010</v>
       </c>
       <c r="D3" t="inlineStr">
         <is>

--- a/artfynd/A 21037-2021 artfynd.xlsx
+++ b/artfynd/A 21037-2021 artfynd.xlsx
@@ -804,7 +804,7 @@
         <v>128635232</v>
       </c>
       <c r="B3" t="n">
-        <v>87010</v>
+        <v>87014</v>
       </c>
       <c r="D3" t="inlineStr">
         <is>

--- a/artfynd/A 21037-2021 artfynd.xlsx
+++ b/artfynd/A 21037-2021 artfynd.xlsx
@@ -910,7 +910,7 @@
         <v>130171749</v>
       </c>
       <c r="B4" t="n">
-        <v>106183</v>
+        <v>106186</v>
       </c>
       <c r="D4" t="inlineStr">
         <is>
@@ -997,7 +997,7 @@
       </c>
       <c r="AX4" t="inlineStr">
         <is>
-          <t>Fredrik Larsson, Henrik Weibull</t>
+          <t>Henrik Weibull, Fredrik Larsson</t>
         </is>
       </c>
       <c r="AY4" t="inlineStr"/>
@@ -1007,7 +1007,7 @@
         <v>130171746</v>
       </c>
       <c r="B5" t="n">
-        <v>95950</v>
+        <v>95952</v>
       </c>
       <c r="D5" t="inlineStr">
         <is>
@@ -1094,7 +1094,7 @@
       </c>
       <c r="AX5" t="inlineStr">
         <is>
-          <t>Fredrik Larsson, Henrik Weibull</t>
+          <t>Henrik Weibull, Fredrik Larsson</t>
         </is>
       </c>
       <c r="AY5" t="inlineStr"/>
@@ -1104,7 +1104,7 @@
         <v>130171750</v>
       </c>
       <c r="B6" t="n">
-        <v>95905</v>
+        <v>95907</v>
       </c>
       <c r="D6" t="inlineStr">
         <is>
@@ -1191,7 +1191,7 @@
       </c>
       <c r="AX6" t="inlineStr">
         <is>
-          <t>Fredrik Larsson, Henrik Weibull</t>
+          <t>Henrik Weibull, Fredrik Larsson</t>
         </is>
       </c>
       <c r="AY6" t="inlineStr"/>

--- a/artfynd/A 21037-2021 artfynd.xlsx
+++ b/artfynd/A 21037-2021 artfynd.xlsx
@@ -910,7 +910,7 @@
         <v>130171749</v>
       </c>
       <c r="B4" t="n">
-        <v>106186</v>
+        <v>106273</v>
       </c>
       <c r="D4" t="inlineStr">
         <is>
@@ -1007,7 +1007,7 @@
         <v>130171746</v>
       </c>
       <c r="B5" t="n">
-        <v>95952</v>
+        <v>96039</v>
       </c>
       <c r="D5" t="inlineStr">
         <is>
@@ -1104,7 +1104,7 @@
         <v>130171750</v>
       </c>
       <c r="B6" t="n">
-        <v>95907</v>
+        <v>95994</v>
       </c>
       <c r="D6" t="inlineStr">
         <is>

--- a/artfynd/A 21037-2021 artfynd.xlsx
+++ b/artfynd/A 21037-2021 artfynd.xlsx
@@ -910,7 +910,7 @@
         <v>130171749</v>
       </c>
       <c r="B4" t="n">
-        <v>106273</v>
+        <v>106276</v>
       </c>
       <c r="D4" t="inlineStr">
         <is>
@@ -1007,7 +1007,7 @@
         <v>130171746</v>
       </c>
       <c r="B5" t="n">
-        <v>96039</v>
+        <v>96042</v>
       </c>
       <c r="D5" t="inlineStr">
         <is>
@@ -1104,7 +1104,7 @@
         <v>130171750</v>
       </c>
       <c r="B6" t="n">
-        <v>95994</v>
+        <v>95997</v>
       </c>
       <c r="D6" t="inlineStr">
         <is>

--- a/artfynd/A 21037-2021 artfynd.xlsx
+++ b/artfynd/A 21037-2021 artfynd.xlsx
@@ -910,7 +910,7 @@
         <v>130171749</v>
       </c>
       <c r="B4" t="n">
-        <v>106276</v>
+        <v>106302</v>
       </c>
       <c r="D4" t="inlineStr">
         <is>
@@ -1007,7 +1007,7 @@
         <v>130171746</v>
       </c>
       <c r="B5" t="n">
-        <v>96042</v>
+        <v>96068</v>
       </c>
       <c r="D5" t="inlineStr">
         <is>
@@ -1104,7 +1104,7 @@
         <v>130171750</v>
       </c>
       <c r="B6" t="n">
-        <v>95997</v>
+        <v>96023</v>
       </c>
       <c r="D6" t="inlineStr">
         <is>

--- a/artfynd/A 21037-2021 artfynd.xlsx
+++ b/artfynd/A 21037-2021 artfynd.xlsx
@@ -910,7 +910,7 @@
         <v>130171749</v>
       </c>
       <c r="B4" t="n">
-        <v>106302</v>
+        <v>106303</v>
       </c>
       <c r="D4" t="inlineStr">
         <is>
@@ -1007,7 +1007,7 @@
         <v>130171746</v>
       </c>
       <c r="B5" t="n">
-        <v>96068</v>
+        <v>96069</v>
       </c>
       <c r="D5" t="inlineStr">
         <is>
@@ -1104,7 +1104,7 @@
         <v>130171750</v>
       </c>
       <c r="B6" t="n">
-        <v>96023</v>
+        <v>96024</v>
       </c>
       <c r="D6" t="inlineStr">
         <is>

--- a/artfynd/A 21037-2021 artfynd.xlsx
+++ b/artfynd/A 21037-2021 artfynd.xlsx
@@ -910,7 +910,7 @@
         <v>130171749</v>
       </c>
       <c r="B4" t="n">
-        <v>106303</v>
+        <v>106304</v>
       </c>
       <c r="D4" t="inlineStr">
         <is>
@@ -1007,7 +1007,7 @@
         <v>130171746</v>
       </c>
       <c r="B5" t="n">
-        <v>96069</v>
+        <v>96070</v>
       </c>
       <c r="D5" t="inlineStr">
         <is>
@@ -1104,7 +1104,7 @@
         <v>130171750</v>
       </c>
       <c r="B6" t="n">
-        <v>96024</v>
+        <v>96025</v>
       </c>
       <c r="D6" t="inlineStr">
         <is>

--- a/artfynd/A 21037-2021 artfynd.xlsx
+++ b/artfynd/A 21037-2021 artfynd.xlsx
@@ -910,7 +910,7 @@
         <v>130171749</v>
       </c>
       <c r="B4" t="n">
-        <v>106304</v>
+        <v>106306</v>
       </c>
       <c r="D4" t="inlineStr">
         <is>
@@ -997,7 +997,7 @@
       </c>
       <c r="AX4" t="inlineStr">
         <is>
-          <t>Henrik Weibull, Fredrik Larsson</t>
+          <t>Fredrik Larsson, Henrik Weibull</t>
         </is>
       </c>
       <c r="AY4" t="inlineStr"/>
@@ -1007,7 +1007,7 @@
         <v>130171746</v>
       </c>
       <c r="B5" t="n">
-        <v>96070</v>
+        <v>96072</v>
       </c>
       <c r="D5" t="inlineStr">
         <is>
@@ -1094,7 +1094,7 @@
       </c>
       <c r="AX5" t="inlineStr">
         <is>
-          <t>Henrik Weibull, Fredrik Larsson</t>
+          <t>Fredrik Larsson, Henrik Weibull</t>
         </is>
       </c>
       <c r="AY5" t="inlineStr"/>
@@ -1104,7 +1104,7 @@
         <v>130171750</v>
       </c>
       <c r="B6" t="n">
-        <v>96025</v>
+        <v>96027</v>
       </c>
       <c r="D6" t="inlineStr">
         <is>
@@ -1191,7 +1191,7 @@
       </c>
       <c r="AX6" t="inlineStr">
         <is>
-          <t>Henrik Weibull, Fredrik Larsson</t>
+          <t>Fredrik Larsson, Henrik Weibull</t>
         </is>
       </c>
       <c r="AY6" t="inlineStr"/>
